--- a/data/reports/2024-04-30/2024-04-30_duplicates.xlsx
+++ b/data/reports/2024-04-30/2024-04-30_duplicates.xlsx
@@ -85,6 +85,49 @@
     <t>filing_url</t>
   </si>
   <si>
+    <t>RMD0004807</t>
+  </si>
+  <si>
+    <t>e-vergent.com, LLC</t>
+  </si>
+  <si>
+    <t>2524 76th St
+Franksville WI 53126</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>United States of America</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>Shawn Tarlo</t>
+  </si>
+  <si>
+    <t>Technical Support Lead</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>2628983786</t>
+  </si>
+  <si>
+    <t>Complete STIR/SHAKEN Implementation</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>2024-04-02</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0004801</t>
   </si>
   <si>
@@ -95,54 +138,11 @@
 Franksville Wisconsin 53126</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>United States of America</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
     <t>null
 null</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=949115a61bc13c102eb2a82fe54bcb0c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004807</t>
-  </si>
-  <si>
-    <t>e-vergent.com, LLC</t>
-  </si>
-  <si>
-    <t>2524 76th St
-Franksville WI 53126</t>
-  </si>
-  <si>
-    <t>Shawn Tarlo</t>
-  </si>
-  <si>
-    <t>Technical Support Lead</t>
-  </si>
-  <si>
-    <t>Support</t>
-  </si>
-  <si>
-    <t>2628983786</t>
-  </si>
-  <si>
-    <t>Complete STIR/SHAKEN Implementation</t>
-  </si>
-  <si>
-    <t>2024-04-02</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005813</t>
@@ -185,7 +185,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004139</t>
+    <t>RMD0009352</t>
   </si>
   <si>
     <t>Global Net Holdings, Inc.</t>
@@ -201,34 +201,56 @@
     <t>CEO</t>
   </si>
   <si>
+    <t>Financial</t>
+  </si>
+  <si>
+    <t>800-7096314</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004139</t>
+  </si>
+  <si>
     <t>Sales</t>
   </si>
   <si>
     <t>800-709-6314</t>
   </si>
   <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c77b62251b09741002beea82f54bcb87&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009352</t>
-  </si>
-  <si>
-    <t>Financial</t>
-  </si>
-  <si>
-    <t>800-7096314</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
+    <t>RMD0008972</t>
+  </si>
+  <si>
+    <t>Media Flint, Inc.</t>
+  </si>
+  <si>
+    <t>15260 Ventura Boulevard
+Suite 1200 PMB 492
+Sherman Oaks California 91403</t>
+  </si>
+  <si>
+    <t>U.S. Virgin Islands</t>
+  </si>
+  <si>
+    <t>AvidTrak</t>
+  </si>
+  <si>
+    <t>null
+null CA
+California</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008973</t>
-  </si>
-  <si>
-    <t>Media Flint, Inc.</t>
   </si>
   <si>
     <t>15260 Ventura Boulevard
@@ -236,32 +258,10 @@
 Sherman Oaks CA 91403</t>
   </si>
   <si>
-    <t>U.S. Virgin Islands</t>
-  </si>
-  <si>
-    <t>AvidTrak</t>
-  </si>
-  <si>
-    <t>null
-null CA
-California</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008972</t>
-  </si>
-  <si>
-    <t>15260 Ventura Boulevard
-Suite 1200 PMB 492
-Sherman Oaks California 91403</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009020</t>
+    <t>RMD0009019</t>
   </si>
   <si>
     <t>Enhanced Telecommunications &amp; Data, Inc.</t>
@@ -277,6 +277,24 @@
     <t>Engineer</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>208-947-3900</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>2024-04-09</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009020</t>
+  </si>
+  <si>
     <t>IT Department</t>
   </si>
   <si>
@@ -284,24 +302,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009019</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>208-947-3900</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>2024-04-09</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009205</t>
@@ -346,7 +346,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008869</t>
+    <t>RMD0006774</t>
   </si>
   <si>
     <t>Sage Communications, Inc.</t>
@@ -356,9 +356,18 @@
 Camarillo CA 93012</t>
   </si>
   <si>
+    <t>NONE</t>
+  </si>
+  <si>
     <t>Sage Network &amp; Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008869</t>
+  </si>
+  <si>
     <t>Rick Minyard</t>
   </si>
   <si>
@@ -380,16 +389,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0006774</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004389</t>
+    <t>RMD0003929</t>
   </si>
   <si>
     <t>Idealtel Dominicana USA, Inc. dba myidealtel.com</t>
@@ -400,13 +400,13 @@
 Cooper City FL 33328</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fab855e51b09741064c4426de54bcbf6&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004389</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9a075a791b8db4109294113d9c4bcbd5&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003929</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fab855e51b09741064c4426de54bcbf6&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005819</t>
@@ -493,10 +493,44 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0007488</t>
+  </si>
+  <si>
+    <t>Matchcom Telecommunications Inc.</t>
+  </si>
+  <si>
+    <t>1680 Michigan Ave
+Ste 700
+Miami Beach FL 33139</t>
+  </si>
+  <si>
+    <t>Cesar Luna</t>
+  </si>
+  <si>
+    <t>NOC Manager</t>
+  </si>
+  <si>
+    <t>NOC Department</t>
+  </si>
+  <si>
+    <t>1680 Michigan Avenue
+Suite 700
+Miami FL 33139</t>
+  </si>
+  <si>
+    <t>9544563191</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2023-12-18</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=267cc9661b3ef410aa3cea41f54bcbcd&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0003758</t>
-  </si>
-  <si>
-    <t>Matchcom Telecommunications Inc.</t>
   </si>
   <si>
     <t>1680 Michigan Ave
@@ -523,40 +557,6 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007488</t>
-  </si>
-  <si>
-    <t>1680 Michigan Ave
-Ste 700
-Miami Beach FL 33139</t>
-  </si>
-  <si>
-    <t>Cesar Luna</t>
-  </si>
-  <si>
-    <t>NOC Manager</t>
-  </si>
-  <si>
-    <t>NOC Department</t>
-  </si>
-  <si>
-    <t>1680 Michigan Avenue
-Suite 700
-Miami FL 33139</t>
-  </si>
-  <si>
-    <t>9544563191</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2023-12-18</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=267cc9661b3ef410aa3cea41f54bcbcd&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0004110</t>
   </si>
   <si>
@@ -593,7 +593,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9650dd421bcd38102eb2a82fe54bcb46&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005139</t>
+    <t>RMD0005124</t>
   </si>
   <si>
     <t>Opentact Inc</t>
@@ -604,6 +604,12 @@
 Cheyenne WY 82009</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f40ce7d11b8eb01068d1a82eac4bcbde&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005139</t>
+  </si>
+  <si>
     <t>Anne Kwong</t>
   </si>
   <si>
@@ -626,31 +632,43 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=89cc84f51b4af01068d1a82eac4bcb3e&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005124</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f40ce7d11b8eb01068d1a82eac4bcbde&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004701</t>
-  </si>
-  <si>
-    <t>Jaintel LLC</t>
+    <t>RMD0003052</t>
+  </si>
+  <si>
+    <t>Jaintel Limited</t>
   </si>
   <si>
     <t>24A Trolley Square #1685
 DE 19806-3334 Wilmington, United States</t>
   </si>
   <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>Elayaraja Jinadoss</t>
   </si>
   <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>'+447341664829</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004701</t>
+  </si>
+  <si>
+    <t>Jaintel LLC</t>
+  </si>
+  <si>
     <t>Operations Director</t>
   </si>
   <si>
-    <t>Management</t>
-  </si>
-  <si>
     <t>'+1 737 237 0913</t>
   </si>
   <si>
@@ -658,24 +676,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b1f3904a1b4138107ccf20ecac4bcbbf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003052</t>
-  </si>
-  <si>
-    <t>Jaintel Limited</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>'+447341664829</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0003053</t>
@@ -706,7 +706,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1e7857331b4885103e8aa93be54bcb79&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003444</t>
+    <t>RMD0003442</t>
   </si>
   <si>
     <t>Shaw Telecom GP</t>
@@ -717,32 +717,6 @@
   </si>
   <si>
     <t>Canada</t>
-  </si>
-  <si>
-    <t>0031064868; 0031064884; 0031064900</t>
-  </si>
-  <si>
-    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
-  </si>
-  <si>
-    <t>Network Operations</t>
-  </si>
-  <si>
-    <t>TOPS-NR&amp;A</t>
-  </si>
-  <si>
-    <t>2728 Hopewell Place N.E.
-Calgary AE 17724
-Alberta</t>
-  </si>
-  <si>
-    <t>'+1-866-244-7475</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003442</t>
   </si>
   <si>
     <t>0031064868;
@@ -762,6 +736,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=322c4e941b8df0509294113d9c4bcb51&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0003444</t>
+  </si>
+  <si>
+    <t>0031064868; 0031064884; 0031064900</t>
+  </si>
+  <si>
+    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
+  </si>
+  <si>
+    <t>Network Operations</t>
+  </si>
+  <si>
+    <t>TOPS-NR&amp;A</t>
+  </si>
+  <si>
+    <t>2728 Hopewell Place N.E.
+Calgary AE 17724
+Alberta</t>
+  </si>
+  <si>
+    <t>'+1-866-244-7475</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0007384</t>
   </si>
   <si>
@@ -790,7 +790,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005040</t>
+    <t>RMD0008577</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -800,31 +800,31 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>BatchDialer</t>
+  </si>
+  <si>
+    <t>Ivo Draginov</t>
+  </si>
+  <si>
+    <t>Product Manager</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>6026220397</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005040</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008577</t>
-  </si>
-  <si>
-    <t>BatchDialer</t>
-  </si>
-  <si>
-    <t>Ivo Draginov</t>
-  </si>
-  <si>
-    <t>Product Manager</t>
-  </si>
-  <si>
-    <t>Operations</t>
-  </si>
-  <si>
-    <t>6026220397</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005569</t>
+    <t>RMD0005461</t>
   </si>
   <si>
     <t>Valstarr Asia</t>
@@ -834,25 +834,10 @@
 Valley Center CA 92082</t>
   </si>
   <si>
+    <t>0031217672</t>
+  </si>
+  <si>
     <t>Vincent W. Kahn</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Systems Admin</t>
-  </si>
-  <si>
-    <t>'+13213288217</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=93ebdbd01b227810ca5aec21f54bcbd6&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005461</t>
-  </si>
-  <si>
-    <t>0031217672</t>
   </si>
   <si>
     <t>MANAGER</t>
@@ -872,7 +857,22 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612913461bd6f010ca5aec21f54bcbac&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005297</t>
+    <t>RMD0005569</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>Systems Admin</t>
+  </si>
+  <si>
+    <t>'+13213288217</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=93ebdbd01b227810ca5aec21f54bcbd6&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007936</t>
   </si>
   <si>
     <t>STREAMLINE SELLERS PTY LTD</t>
@@ -885,22 +885,22 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Syed Omar Farooq Shah</t>
+  </si>
+  <si>
+    <t>'+61406851546</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005297</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007936</t>
-  </si>
-  <si>
-    <t>Syed Omar Farooq Shah</t>
-  </si>
-  <si>
-    <t>'+61406851546</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005574</t>
+    <t>RMD0005585</t>
   </si>
   <si>
     <t>MegaClec, Inc</t>
@@ -914,6 +914,28 @@
     <t>0012465480</t>
   </si>
   <si>
+    <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
+  </si>
+  <si>
+    <t>Paul Joncas</t>
+  </si>
+  <si>
+    <t>Operatopms</t>
+  </si>
+  <si>
+    <t>187 Plymouth Avenue
+Fall River MA 02721</t>
+  </si>
+  <si>
+    <t>5086460030</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005574</t>
+  </si>
+  <si>
     <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
   </si>
   <si>
@@ -921,29 +943,7 @@
 Fall River MA 02721</t>
   </si>
   <si>
-    <t>5086460030</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005585</t>
-  </si>
-  <si>
-    <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
-  </si>
-  <si>
-    <t>Paul Joncas</t>
-  </si>
-  <si>
-    <t>Operatopms</t>
-  </si>
-  <si>
-    <t>187 Plymouth Avenue
-Fall River MA 02721</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007962</t>
@@ -978,7 +978,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3acc71c31b2a305064c4426de54bcb40&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008125</t>
+    <t>RMD0008123</t>
   </si>
   <si>
     <t>Hansen Network Solutions &amp; Services</t>
@@ -989,6 +989,12 @@
 Las Vegas NV 89128</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3cc1fbbe1b7a3810dcd1ed3be54bcbe8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008125</t>
+  </si>
+  <si>
     <t>JR Jarmillo</t>
   </si>
   <si>
@@ -1001,13 +1007,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9277fe1b7a3810dcd1ed3be54bcb40&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008123</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3cc1fbbe1b7a3810dcd1ed3be54bcbe8&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007575</t>
+    <t>RMD0007626</t>
   </si>
   <si>
     <t>Turcios Parada SA</t>
@@ -1020,16 +1020,16 @@
     <t>El Salvador</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5b6a75a61b3af410680f657ae54bcbbd&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007575</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007626</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5b6a75a61b3af410680f657ae54bcbbd&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007716</t>
+    <t>RMD0007696</t>
   </si>
   <si>
     <t>High Country Internet</t>
@@ -1039,16 +1039,16 @@
 Tucson AZ 85719</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007716</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007696</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -1058,6 +1058,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -1071,12 +1077,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008423</t>
@@ -1110,7 +1110,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008451</t>
+    <t>RMD0008450</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1120,12 +1120,6 @@
 Greensboro NC 27401</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008450</t>
-  </si>
-  <si>
     <t>null
 null NC</t>
   </si>
@@ -1133,7 +1127,13 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008612</t>
+    <t>RMD0008451</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008611</t>
   </si>
   <si>
     <t>Liberty Wealth Planners</t>
@@ -1143,6 +1143,18 @@
  110065 Dehli, India</t>
   </si>
   <si>
+    <t>Bangladesh</t>
+  </si>
+  <si>
+    <t>Nobe</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008612</t>
+  </si>
+  <si>
     <t>India</t>
   </si>
   <si>
@@ -1158,19 +1170,7 @@
     <t>RMD0008610</t>
   </si>
   <si>
-    <t>Bangladesh</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008611</t>
-  </si>
-  <si>
-    <t>Nobe</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008759</t>
@@ -1235,34 +1235,34 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=82b1054a1b0f30508d57ecace54bcbda&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008787</t>
+  </si>
+  <si>
+    <t>Personal Computers Plus</t>
+  </si>
+  <si>
+    <t>0031485048</t>
+  </si>
+  <si>
+    <t>Jeffrey Houston</t>
+  </si>
+  <si>
+    <t>Networking</t>
+  </si>
+  <si>
+    <t>'+16039294272</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3752aec61b0f3050003c43f1f54bcb54&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008786</t>
   </si>
   <si>
-    <t>Personal Computers Plus</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=29f1aec61b0f3050003c43f1f54bcba5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008787</t>
-  </si>
-  <si>
-    <t>0031485048</t>
-  </si>
-  <si>
-    <t>Jeffrey Houston</t>
-  </si>
-  <si>
-    <t>Networking</t>
-  </si>
-  <si>
-    <t>'+16039294272</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3752aec61b0f3050003c43f1f54bcb54&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009161</t>
+    <t>RMD0009160</t>
   </si>
   <si>
     <t>MCE Systems</t>
@@ -1272,16 +1272,16 @@
 Irvine CA 92604</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009161</t>
+  </si>
+  <si>
     <t>9497014500</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=2338b76a1b577410503110ad9c4bcb43&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009160</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009453</t>
@@ -6054,42 +6054,56 @@
       <c r="I3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="M3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
+      <c r="Q3" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R3" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U3" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="V3" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B4" s="1">
         <v>16082927</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>26</v>
@@ -6106,40 +6120,26 @@
       <c r="I4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
       <c r="M4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>38</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
       <c r="P4" s="1"/>
-      <c r="Q4" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="Q4" s="1"/>
       <c r="R4" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>40</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U4" s="1"/>
       <c r="V4" s="1" t="s">
         <v>41</v>
       </c>
@@ -6236,7 +6236,7 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -6249,7 +6249,7 @@
         <v>26</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1" t="s">
@@ -6275,9 +6275,15 @@
       <c r="F7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
+      <c r="G7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J7" s="1" t="s">
         <v>58</v>
       </c>
@@ -6298,10 +6304,10 @@
       </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>26</v>
@@ -6335,15 +6341,9 @@
       <c r="F8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
         <v>58</v>
       </c>
@@ -6364,10 +6364,10 @@
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>26</v>
@@ -6396,7 +6396,7 @@
         <v>70</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>71</v>
@@ -6423,7 +6423,7 @@
         <v>26</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="1" t="s">
@@ -6444,7 +6444,7 @@
         <v>76</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>71</v>
@@ -6471,7 +6471,7 @@
         <v>26</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U10" s="1"/>
       <c r="V10" s="1" t="s">
@@ -6518,12 +6518,14 @@
       <c r="O11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="Q11" s="1" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S11" s="1" t="s">
         <v>26</v>
@@ -6531,14 +6533,16 @@
       <c r="T11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="V11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1">
         <v>21520390</v>
@@ -6565,7 +6569,7 @@
         <v>82</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>80</v>
@@ -6574,16 +6578,14 @@
         <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>26</v>
@@ -6591,9 +6593,7 @@
       <c r="T12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="U12" s="1"/>
       <c r="V12" s="1" t="s">
         <v>91</v>
       </c>
@@ -6645,7 +6645,7 @@
         <v>101</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>26</v>
@@ -6672,7 +6672,7 @@
         <v>94</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>71</v>
@@ -6697,7 +6697,7 @@
         <v>26</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1" t="s">
@@ -6723,54 +6723,40 @@
       <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1">
         <v>23250467</v>
@@ -6787,33 +6773,47 @@
       <c r="F16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U16" s="1"/>
       <c r="V16" s="1" t="s">
         <v>118</v>
       </c>
@@ -6844,7 +6844,7 @@
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -6857,7 +6857,7 @@
         <v>26</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U17" s="1"/>
       <c r="V17" s="1" t="s">
@@ -6890,7 +6890,7 @@
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
@@ -6903,7 +6903,7 @@
         <v>26</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U18" s="1"/>
       <c r="V18" s="1" t="s">
@@ -6994,7 +6994,7 @@
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
@@ -7007,7 +7007,7 @@
         <v>26</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U20" s="1"/>
       <c r="V20" s="1" t="s">
@@ -7051,7 +7051,7 @@
         <v>26</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U21" s="1" t="s">
         <v>135</v>
@@ -7102,16 +7102,16 @@
       </c>
       <c r="P22" s="1"/>
       <c r="Q22" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U22" s="1" t="s">
         <v>142</v>
@@ -7134,7 +7134,7 @@
         <v>146</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>71</v>
@@ -7146,7 +7146,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
@@ -7159,7 +7159,7 @@
         <v>26</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U23" s="1"/>
       <c r="V23" s="1" t="s">
@@ -7180,7 +7180,7 @@
         <v>149</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>71</v>
@@ -7192,7 +7192,7 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
@@ -7205,7 +7205,7 @@
         <v>26</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U24" s="1"/>
       <c r="V24" s="1" t="s">
@@ -7252,9 +7252,11 @@
       <c r="O25" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="P25" s="1"/>
+      <c r="P25" s="1" t="s">
+        <v>159</v>
+      </c>
       <c r="Q25" s="1" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>26</v>
@@ -7263,16 +7265,18 @@
         <v>26</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U25" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>160</v>
+      </c>
       <c r="V25" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="A26" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B26" s="1">
         <v>27710730</v>
@@ -7281,7 +7285,7 @@
         <v>152</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>26</v>
@@ -7293,28 +7297,26 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>27</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>167</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>26</v>
@@ -7323,11 +7325,9 @@
         <v>26</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U26" s="1" t="s">
-        <v>168</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U26" s="1"/>
       <c r="V26" s="1" t="s">
         <v>169</v>
       </c>
@@ -7364,7 +7364,7 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
@@ -7377,7 +7377,7 @@
         <v>26</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U27" s="1"/>
       <c r="V27" s="1" t="s">
@@ -7419,7 +7419,7 @@
         <v>176</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>177</v>
@@ -7432,10 +7432,10 @@
       </c>
       <c r="P28" s="1"/>
       <c r="Q28" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>26</v>
@@ -7478,47 +7478,33 @@
       <c r="I29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U29" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="V29" s="1" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B30" s="1">
         <v>30149645</v>
@@ -7544,26 +7530,40 @@
       <c r="I30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
+      <c r="J30" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>188</v>
+      </c>
       <c r="M30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
+        <v>189</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>190</v>
+      </c>
       <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
+      <c r="Q30" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R30" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U30" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U30" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="V30" s="1" t="s">
         <v>192</v>
       </c>
@@ -7582,48 +7582,52 @@
         <v>195</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
+        <v>196</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="J31" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>195</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>27</v>
+        <v>196</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P31" s="1"/>
       <c r="Q31" s="1" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U31" s="1" t="s">
-        <v>200</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U31" s="1"/>
       <c r="V31" s="1" t="s">
         <v>201</v>
       </c>
@@ -7642,52 +7646,48 @@
         <v>195</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="L32" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>195</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>204</v>
+        <v>27</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P32" s="1"/>
       <c r="Q32" s="1" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U32" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>206</v>
+      </c>
       <c r="V32" s="1" t="s">
         <v>207</v>
       </c>
@@ -7706,10 +7706,10 @@
         <v>210</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -7718,7 +7718,7 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
@@ -7731,7 +7731,7 @@
         <v>26</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U33" s="1"/>
       <c r="V33" s="1" t="s">
@@ -7752,10 +7752,10 @@
         <v>210</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
@@ -7773,7 +7773,7 @@
         <v>210</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="O34" s="1" t="s">
         <v>215</v>
@@ -7783,7 +7783,7 @@
         <v>101</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>26</v>
@@ -7810,7 +7810,7 @@
         <v>219</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>220</v>
@@ -7822,45 +7822,33 @@
       <c r="I35" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>224</v>
-      </c>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
       <c r="M35" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>226</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
       <c r="P35" s="1"/>
-      <c r="Q35" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q35" s="1"/>
       <c r="R35" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U35" s="1"/>
       <c r="V35" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B36" s="1">
         <v>31064850</v>
@@ -7872,36 +7860,48 @@
         <v>219</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>220</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="O36" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
       <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
+      <c r="Q36" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R36" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U36" s="1"/>
       <c r="V36" s="1" t="s">
@@ -7922,7 +7922,7 @@
         <v>234</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>235</v>
@@ -7953,7 +7953,7 @@
         <v>51</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>26</v>
@@ -7980,7 +7980,7 @@
         <v>234</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>235</v>
@@ -7992,7 +7992,7 @@
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
@@ -8005,7 +8005,7 @@
         <v>26</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
@@ -8033,34 +8033,48 @@
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
+      <c r="I39" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>247</v>
+      </c>
       <c r="M39" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
+        <v>243</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>248</v>
+      </c>
       <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
+      <c r="Q39" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R39" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U39" s="1"/>
       <c r="V39" s="1" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B40" s="1">
         <v>31124688</v>
@@ -8079,39 +8093,25 @@
       </c>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
-      <c r="I40" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>249</v>
-      </c>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
       <c r="M40" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>250</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
       <c r="P40" s="1"/>
-      <c r="Q40" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="Q40" s="1"/>
       <c r="R40" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U40" s="1"/>
       <c r="V40" s="1" t="s">
@@ -8137,48 +8137,54 @@
       <c r="F41" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
+      <c r="G41" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J41" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>27</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="P41" s="1"/>
       <c r="Q41" s="1" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U41" s="1"/>
       <c r="V41" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B42" s="1">
         <v>31217029</v>
@@ -8195,26 +8201,20 @@
       <c r="F42" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
       <c r="J42" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>27</v>
@@ -8224,16 +8224,16 @@
       </c>
       <c r="P42" s="1"/>
       <c r="Q42" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
@@ -8254,7 +8254,7 @@
         <v>269</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>270</v>
@@ -8262,33 +8262,45 @@
       <c r="G43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
+      <c r="J43" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>214</v>
+      </c>
       <c r="M43" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
+        <v>269</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>272</v>
+      </c>
       <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
+      <c r="Q43" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R43" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B44" s="1">
         <v>31294614</v>
@@ -8300,7 +8312,7 @@
         <v>269</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>270</v>
@@ -8308,36 +8320,24 @@
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-      <c r="J44" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>214</v>
-      </c>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>274</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
       <c r="P44" s="1"/>
-      <c r="Q44" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q44" s="1"/>
       <c r="R44" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U44" s="1"/>
       <c r="V44" s="1" t="s">
@@ -8369,42 +8369,48 @@
       <c r="H45" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>282</v>
+      </c>
       <c r="M45" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>27</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P45" s="1"/>
       <c r="Q45" s="1" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U45" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U45" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="V45" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B46" s="1">
         <v>31356652</v>
@@ -8425,18 +8431,14 @@
         <v>279</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L46" s="1" t="s">
         <v>287</v>
       </c>
+      <c r="I46" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
       <c r="M46" s="1" t="s">
         <v>288</v>
       </c>
@@ -8444,24 +8446,22 @@
         <v>27</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P46" s="1"/>
       <c r="Q46" s="1" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S46" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U46" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U46" s="1"/>
       <c r="V46" s="1" t="s">
         <v>289</v>
       </c>
@@ -8478,7 +8478,7 @@
         <v>291</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>292</v>
@@ -8509,7 +8509,7 @@
         <v>101</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S47" s="1" t="s">
         <v>26</v>
@@ -8534,7 +8534,7 @@
         <v>298</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>292</v>
@@ -8552,7 +8552,7 @@
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
@@ -8565,7 +8565,7 @@
         <v>26</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U48" s="1"/>
       <c r="V48" s="1" t="s">
@@ -8586,55 +8586,41 @@
         <v>302</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
-      <c r="J49" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
       <c r="M49" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O49" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="P49" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
       <c r="R49" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S49" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U49" s="1"/>
       <c r="V49" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="50" spans="1:22">
       <c r="A50" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B50" s="1">
         <v>31394760</v>
@@ -8646,32 +8632,46 @@
         <v>302</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
+      <c r="J50" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="L50" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="M50" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
+        <v>302</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="P50" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q50" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R50" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S50" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U50" s="1"/>
       <c r="V50" s="1" t="s">
@@ -8692,7 +8692,7 @@
         <v>311</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>312</v>
@@ -8703,7 +8703,9 @@
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
+      <c r="M51" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
@@ -8715,7 +8717,7 @@
         <v>26</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U51" s="1"/>
       <c r="V51" s="1" t="s">
@@ -8736,7 +8738,7 @@
         <v>311</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>312</v>
@@ -8747,9 +8749,7 @@
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
-      <c r="M52" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="M52" s="1"/>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
@@ -8761,7 +8761,7 @@
         <v>26</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U52" s="1"/>
       <c r="V52" s="1" t="s">
@@ -8782,25 +8782,19 @@
         <v>318</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
@@ -8813,7 +8807,7 @@
         <v>26</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
@@ -8834,19 +8828,25 @@
         <v>318</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
+      <c r="G54" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
       <c r="M54" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
@@ -8859,7 +8859,7 @@
         <v>26</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -8880,55 +8880,41 @@
         <v>324</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
-      <c r="J55" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
       <c r="M55" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="P55" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
       <c r="R55" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U55" s="1"/>
       <c r="V55" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B56" s="1">
         <v>31445216</v>
@@ -8940,32 +8926,46 @@
         <v>324</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
+      <c r="J56" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="M56" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
-      <c r="Q56" s="1"/>
+        <v>324</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R56" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S56" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U56" s="1"/>
       <c r="V56" s="1" t="s">
@@ -8986,7 +8986,7 @@
         <v>334</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>220</v>
@@ -8998,7 +8998,7 @@
         <v>335</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L57" s="1"/>
       <c r="M57" s="1" t="s">
@@ -9012,10 +9012,10 @@
       </c>
       <c r="P57" s="1"/>
       <c r="Q57" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R57" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>26</v>
@@ -9042,7 +9042,7 @@
         <v>334</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>220</v>
@@ -9054,7 +9054,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
@@ -9067,7 +9067,7 @@
         <v>26</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U58" s="1"/>
       <c r="V58" s="1" t="s">
@@ -9088,7 +9088,7 @@
         <v>343</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>71</v>
@@ -9100,7 +9100,7 @@
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1" t="s">
-        <v>29</v>
+        <v>344</v>
       </c>
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
@@ -9113,16 +9113,16 @@
         <v>26</v>
       </c>
       <c r="T59" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U59" s="1"/>
       <c r="V59" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="60" spans="1:22">
       <c r="A60" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B60" s="1">
         <v>31457815</v>
@@ -9134,7 +9134,7 @@
         <v>343</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>71</v>
@@ -9146,7 +9146,7 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1" t="s">
-        <v>346</v>
+        <v>40</v>
       </c>
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
@@ -9159,7 +9159,7 @@
         <v>26</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1" t="s">
@@ -9180,53 +9180,43 @@
         <v>350</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>351</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1" t="s">
+      <c r="I61" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="K61" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>353</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
       <c r="P61" s="1"/>
-      <c r="Q61" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q61" s="1"/>
       <c r="R61" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="62" spans="1:22">
       <c r="A62" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B62" s="1">
         <v>31475270</v>
@@ -9238,41 +9228,53 @@
         <v>350</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
+      <c r="J62" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="M62" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
+        <v>350</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>357</v>
+      </c>
       <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
+      <c r="Q62" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R62" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U62" s="1"/>
       <c r="V62" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="63" spans="1:22">
       <c r="A63" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B63" s="1">
         <v>31475270</v>
@@ -9284,21 +9286,19 @@
         <v>350</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
-      <c r="I63" s="1" t="s">
-        <v>359</v>
-      </c>
+      <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
       <c r="M63" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
@@ -9311,7 +9311,7 @@
         <v>26</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U63" s="1"/>
       <c r="V63" s="1" t="s">
@@ -9342,7 +9342,7 @@
         <v>363</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L64" s="1"/>
       <c r="M64" s="1" t="s">
@@ -9361,7 +9361,7 @@
         <v>51</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S64" s="1" t="s">
         <v>26</v>
@@ -9386,7 +9386,7 @@
         <v>362</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>71</v>
@@ -9398,7 +9398,7 @@
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
@@ -9411,7 +9411,7 @@
         <v>26</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U65" s="1"/>
       <c r="V65" s="1" t="s">
@@ -9467,7 +9467,7 @@
         <v>51</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>26</v>
@@ -9494,7 +9494,7 @@
         <v>371</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>71</v>
@@ -9508,7 +9508,7 @@
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
@@ -9521,7 +9521,7 @@
         <v>26</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U67" s="1"/>
       <c r="V67" s="1" t="s">
@@ -9542,41 +9542,59 @@
         <v>362</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G68" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>383</v>
+      </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
+      <c r="J68" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>385</v>
+      </c>
       <c r="M68" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
+        <v>362</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R68" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U68" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U68" s="1" t="s">
+        <v>191</v>
+      </c>
       <c r="V68" s="1" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="69" spans="1:22">
       <c r="A69" s="1" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B69" s="1">
         <v>31491517</v>
@@ -9588,52 +9606,34 @@
         <v>362</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>385</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
-      <c r="J69" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>387</v>
-      </c>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
       <c r="M69" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="N69" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O69" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="P69" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1"/>
       <c r="R69" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U69" s="1" t="s">
-        <v>189</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U69" s="1"/>
       <c r="V69" s="1" t="s">
         <v>389</v>
       </c>
@@ -9652,49 +9652,39 @@
         <v>392</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
-      <c r="J70" s="1" t="s">
-        <v>391</v>
-      </c>
+      <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
-      <c r="M70" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="N70" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>393</v>
-      </c>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
       <c r="P70" s="1"/>
-      <c r="Q70" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="Q70" s="1"/>
       <c r="R70" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S70" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U70" s="1"/>
       <c r="V70" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="71" spans="1:22">
       <c r="A71" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B71" s="1">
         <v>31544182</v>
@@ -9706,30 +9696,40 @@
         <v>392</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
+      <c r="J71" s="1" t="s">
+        <v>391</v>
+      </c>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
-      <c r="M71" s="1"/>
-      <c r="N71" s="1"/>
-      <c r="O71" s="1"/>
+      <c r="M71" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>395</v>
+      </c>
       <c r="P71" s="1"/>
-      <c r="Q71" s="1"/>
+      <c r="Q71" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R71" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S71" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U71" s="1"/>
       <c r="V71" s="1" t="s">
@@ -9750,7 +9750,7 @@
         <v>399</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>235</v>
@@ -9773,7 +9773,7 @@
         <v>26</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U72" s="1"/>
       <c r="V72" s="1" t="s">
@@ -9794,7 +9794,7 @@
         <v>402</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>235</v>
@@ -9806,7 +9806,7 @@
         <v>403</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L73" s="1" t="s">
         <v>404</v>
@@ -9825,7 +9825,7 @@
         <v>101</v>
       </c>
       <c r="R73" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S73" s="1" t="s">
         <v>26</v>
@@ -9852,7 +9852,7 @@
         <v>409</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>71</v>
@@ -9875,7 +9875,7 @@
         <v>26</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U74" s="1"/>
       <c r="V74" s="1" t="s">
@@ -9908,7 +9908,7 @@
         <v>412</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L75" s="1" t="s">
         <v>413</v>
@@ -9927,7 +9927,7 @@
         <v>101</v>
       </c>
       <c r="R75" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>26</v>
@@ -9952,7 +9952,7 @@
         <v>417</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>418</v>
@@ -9966,7 +9966,7 @@
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
       <c r="M76" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N76" s="1"/>
       <c r="O76" s="1"/>
@@ -9979,7 +9979,7 @@
         <v>26</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U76" s="1"/>
       <c r="V76" s="1" t="s">
@@ -10002,7 +10002,7 @@
         <v>27</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>422</v>
@@ -10033,7 +10033,7 @@
         <v>51</v>
       </c>
       <c r="R77" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S77" s="1" t="s">
         <v>26</v>
@@ -10058,10 +10058,10 @@
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>28</v>
@@ -10085,7 +10085,7 @@
         <v>432</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O78" s="1" t="s">
         <v>433</v>
@@ -10095,10 +10095,10 @@
         <v>51</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S78" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T78" s="1" t="s">
         <v>26</v>
@@ -10122,7 +10122,7 @@
         <v>437</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>438</v>
@@ -10141,7 +10141,7 @@
         <v>442</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M79" s="1" t="s">
         <v>437</v>
@@ -10154,10 +10154,10 @@
       </c>
       <c r="P79" s="1"/>
       <c r="Q79" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R79" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S79" s="1" t="s">
         <v>26</v>
@@ -10212,10 +10212,10 @@
       </c>
       <c r="P80" s="1"/>
       <c r="Q80" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R80" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S80" s="1" t="s">
         <v>26</v>
@@ -10264,10 +10264,10 @@
       </c>
       <c r="P81" s="1"/>
       <c r="Q81" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S81" s="1" t="s">
         <v>26</v>
@@ -10306,7 +10306,7 @@
         <v>462</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L82" s="1" t="s">
         <v>463</v>
@@ -10325,7 +10325,7 @@
         <v>101</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S82" s="1" t="s">
         <v>26</v>
@@ -10364,10 +10364,10 @@
         <v>469</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M83" s="1" t="s">
         <v>467</v>
@@ -10380,10 +10380,10 @@
       </c>
       <c r="P83" s="1"/>
       <c r="Q83" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R83" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S83" s="1" t="s">
         <v>26</v>
@@ -10420,7 +10420,7 @@
         <v>474</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L84" s="1" t="s">
         <v>475</v>
@@ -10436,10 +10436,10 @@
       </c>
       <c r="P84" s="1"/>
       <c r="Q84" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S84" s="1" t="s">
         <v>26</v>
@@ -10464,7 +10464,7 @@
         <v>480</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>438</v>
@@ -10479,7 +10479,7 @@
         <v>59</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M85" s="1" t="s">
         <v>480</v>
@@ -10492,7 +10492,7 @@
       </c>
       <c r="P85" s="1"/>
       <c r="Q85" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R85" s="1" t="s">
         <v>26</v>
@@ -10501,7 +10501,7 @@
         <v>26</v>
       </c>
       <c r="T85" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U85" s="1"/>
       <c r="V85" s="1" t="s">
@@ -10538,7 +10538,7 @@
         <v>487</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L86" s="1"/>
       <c r="M86" s="1" t="s">
@@ -10561,7 +10561,7 @@
         <v>26</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U86" s="1" t="s">
         <v>489</v>
@@ -10616,10 +10616,10 @@
       </c>
       <c r="P87" s="1"/>
       <c r="Q87" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S87" s="1" t="s">
         <v>26</v>
@@ -10644,7 +10644,7 @@
         <v>499</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>292</v>
@@ -10669,7 +10669,7 @@
         <v>26</v>
       </c>
       <c r="T88" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U88" s="1" t="s">
         <v>501</v>
@@ -10690,7 +10690,7 @@
         <v>504</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>220</v>
@@ -10708,10 +10708,10 @@
         <v>505</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>504</v>
@@ -10727,7 +10727,7 @@
         <v>51</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S89" s="1" t="s">
         <v>26</v>
@@ -10763,10 +10763,10 @@
       </c>
       <c r="I90" s="1"/>
       <c r="J90" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L90" s="1" t="s">
         <v>511</v>
@@ -10782,10 +10782,10 @@
       </c>
       <c r="P90" s="1"/>
       <c r="Q90" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S90" s="1" t="s">
         <v>26</v>
@@ -10810,7 +10810,7 @@
         <v>515</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>516</v>
@@ -10841,7 +10841,7 @@
         <v>101</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S91" s="1" t="s">
         <v>26</v>
@@ -10883,7 +10883,7 @@
         <v>518</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M92" s="1"/>
       <c r="N92" s="1" t="s">
@@ -10900,7 +10900,7 @@
         <v>26</v>
       </c>
       <c r="S92" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T92" s="1" t="s">
         <v>26</v>
@@ -10924,7 +10924,7 @@
         <v>530</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>531</v>
@@ -10939,7 +10939,7 @@
         <v>518</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M93" s="1" t="s">
         <v>530</v>
@@ -10952,10 +10952,10 @@
       </c>
       <c r="P93" s="1"/>
       <c r="Q93" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S93" s="1" t="s">
         <v>26</v>
@@ -10996,10 +10996,10 @@
         <v>539</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M94" s="1" t="s">
         <v>537</v>
@@ -11012,10 +11012,10 @@
       </c>
       <c r="P94" s="1"/>
       <c r="Q94" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S94" s="1" t="s">
         <v>26</v>
@@ -11055,7 +11055,7 @@
         <v>545</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M95" s="1" t="s">
         <v>543</v>
@@ -11068,10 +11068,10 @@
       </c>
       <c r="P95" s="1"/>
       <c r="Q95" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R95" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S95" s="1" t="s">
         <v>26</v>
@@ -11094,10 +11094,10 @@
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
@@ -11109,11 +11109,11 @@
         <v>59</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M96" s="1"/>
       <c r="N96" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="O96" s="1" t="s">
         <v>550</v>
@@ -11123,7 +11123,7 @@
         <v>101</v>
       </c>
       <c r="R96" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S96" s="1" t="s">
         <v>26</v>
@@ -11148,7 +11148,7 @@
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>554</v>
@@ -11174,10 +11174,10 @@
       </c>
       <c r="P97" s="1"/>
       <c r="Q97" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S97" s="1" t="s">
         <v>26</v>
@@ -11210,13 +11210,13 @@
         <v>27</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>563</v>
@@ -11238,10 +11238,10 @@
       </c>
       <c r="P98" s="1"/>
       <c r="Q98" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R98" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S98" s="1" t="s">
         <v>26</v>
@@ -11266,7 +11266,7 @@
         <v>569</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>235</v>
@@ -11278,7 +11278,7 @@
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
       <c r="M99" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
@@ -11291,7 +11291,7 @@
         <v>26</v>
       </c>
       <c r="T99" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U99" s="1"/>
       <c r="V99" s="1" t="s">
@@ -11341,7 +11341,7 @@
         <v>101</v>
       </c>
       <c r="R100" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S100" s="1" t="s">
         <v>26</v>
@@ -11381,7 +11381,7 @@
         <v>374</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M101" s="1" t="s">
         <v>581</v>
@@ -11394,10 +11394,10 @@
       </c>
       <c r="P101" s="1"/>
       <c r="Q101" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R101" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S101" s="1" t="s">
         <v>26</v>
@@ -11436,7 +11436,7 @@
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N102" s="1"/>
       <c r="O102" s="1"/>
@@ -11449,7 +11449,7 @@
         <v>26</v>
       </c>
       <c r="T102" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U102" s="1"/>
       <c r="V102" s="1" t="s">
@@ -11486,7 +11486,7 @@
         <v>590</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L103" s="1" t="s">
         <v>591</v>
@@ -11502,10 +11502,10 @@
       </c>
       <c r="P103" s="1"/>
       <c r="Q103" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R103" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S103" s="1" t="s">
         <v>26</v>
@@ -11532,7 +11532,7 @@
         <v>596</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>235</v>
@@ -11544,7 +11544,7 @@
       <c r="K104" s="1"/>
       <c r="L104" s="1"/>
       <c r="M104" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N104" s="1"/>
       <c r="O104" s="1"/>
@@ -11557,7 +11557,7 @@
         <v>26</v>
       </c>
       <c r="T104" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U104" s="1"/>
       <c r="V104" s="1" t="s">
@@ -11606,10 +11606,10 @@
       </c>
       <c r="P105" s="1"/>
       <c r="Q105" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R105" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S105" s="1" t="s">
         <v>26</v>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="P106" s="1"/>
       <c r="Q106" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R106" s="1" t="s">
         <v>26</v>
@@ -11706,10 +11706,10 @@
         <v>614</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M107" s="1" t="s">
         <v>613</v>
@@ -11722,10 +11722,10 @@
       </c>
       <c r="P107" s="1"/>
       <c r="Q107" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R107" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S107" s="1" t="s">
         <v>26</v>
@@ -11764,10 +11764,10 @@
         <v>620</v>
       </c>
       <c r="K108" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M108" s="1" t="s">
         <v>619</v>
@@ -11783,7 +11783,7 @@
         <v>51</v>
       </c>
       <c r="R108" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S108" s="1" t="s">
         <v>26</v>
@@ -11822,7 +11822,7 @@
         <v>626</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L109" s="1" t="s">
         <v>627</v>
@@ -11838,10 +11838,10 @@
       </c>
       <c r="P109" s="1"/>
       <c r="Q109" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S109" s="1" t="s">
         <v>26</v>
@@ -11866,7 +11866,7 @@
         <v>631</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>220</v>
@@ -11883,7 +11883,7 @@
         <v>82</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M110" s="1" t="s">
         <v>631</v>
@@ -11899,7 +11899,7 @@
         <v>101</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S110" s="1" t="s">
         <v>26</v>
@@ -11922,7 +11922,7 @@
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>637</v>
@@ -11945,7 +11945,7 @@
         <v>26</v>
       </c>
       <c r="T111" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U111" s="1" t="s">
         <v>638</v>
@@ -11981,7 +11981,7 @@
         <v>643</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M112" s="1"/>
       <c r="N112" s="1" t="s">
@@ -11992,10 +11992,10 @@
       </c>
       <c r="P112" s="1"/>
       <c r="Q112" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R112" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S112" s="1" t="s">
         <v>26</v>
@@ -12020,7 +12020,7 @@
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
       <c r="E113" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>292</v>
@@ -12049,7 +12049,7 @@
         <v>26</v>
       </c>
       <c r="T113" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U113" s="1" t="s">
         <v>648</v>
@@ -12068,7 +12068,7 @@
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
       <c r="E114" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>292</v>
@@ -12097,7 +12097,7 @@
         <v>26</v>
       </c>
       <c r="T114" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U114" s="1" t="s">
         <v>648</v>
@@ -12130,10 +12130,10 @@
         <v>655</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M115" s="1"/>
       <c r="N115" s="1" t="s">
@@ -12146,10 +12146,10 @@
         <v>657</v>
       </c>
       <c r="Q115" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R115" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S115" s="1" t="s">
         <v>26</v>
@@ -12176,7 +12176,7 @@
         <v>661</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>662</v>
@@ -12213,7 +12213,7 @@
         <v>101</v>
       </c>
       <c r="R116" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S116" s="1" t="s">
         <v>26</v>
@@ -12256,7 +12256,7 @@
         <v>671</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L117" s="1" t="s">
         <v>672</v>
@@ -12272,10 +12272,10 @@
       </c>
       <c r="P117" s="1"/>
       <c r="Q117" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R117" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S117" s="1" t="s">
         <v>26</v>
@@ -12326,10 +12326,10 @@
       </c>
       <c r="P118" s="1"/>
       <c r="Q118" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R118" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S118" s="1" t="s">
         <v>26</v>
@@ -12388,10 +12388,10 @@
       </c>
       <c r="P119" s="1"/>
       <c r="Q119" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R119" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S119" s="1" t="s">
         <v>26</v>
@@ -12428,7 +12428,7 @@
         <v>690</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L120" s="1" t="s">
         <v>691</v>
@@ -12444,10 +12444,10 @@
       </c>
       <c r="P120" s="1"/>
       <c r="Q120" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R120" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S120" s="1" t="s">
         <v>26</v>
@@ -12470,10 +12470,10 @@
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
@@ -12482,14 +12482,14 @@
         <v>695</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="L121" s="1" t="s">
         <v>214</v>
       </c>
       <c r="M121" s="1"/>
       <c r="N121" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O121" s="1" t="s">
         <v>696</v>
@@ -12499,7 +12499,7 @@
         <v>51</v>
       </c>
       <c r="R121" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S121" s="1" t="s">
         <v>26</v>
@@ -12544,7 +12544,7 @@
         <v>702</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L122" s="1" t="s">
         <v>98</v>
@@ -12563,7 +12563,7 @@
         <v>101</v>
       </c>
       <c r="R122" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S122" s="1" t="s">
         <v>26</v>
@@ -12572,7 +12572,7 @@
         <v>26</v>
       </c>
       <c r="U122" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V122" s="1" t="s">
         <v>704</v>
@@ -12590,10 +12590,10 @@
         <v>706</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>28</v>
@@ -12617,17 +12617,17 @@
         <v>706</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O123" s="1" t="s">
         <v>710</v>
       </c>
       <c r="P123" s="1"/>
       <c r="Q123" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R123" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S123" s="1" t="s">
         <v>26</v>
@@ -12664,10 +12664,10 @@
         <v>714</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M124" s="1" t="s">
         <v>715</v>
@@ -12683,7 +12683,7 @@
         <v>101</v>
       </c>
       <c r="R124" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S124" s="1" t="s">
         <v>26</v>
@@ -12722,7 +12722,7 @@
         <v>721</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L125" s="1" t="s">
         <v>214</v>
@@ -12738,10 +12738,10 @@
       </c>
       <c r="P125" s="1"/>
       <c r="Q125" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R125" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S125" s="1" t="s">
         <v>26</v>
@@ -12764,7 +12764,7 @@
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
       <c r="E126" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>726</v>
@@ -12796,10 +12796,10 @@
       </c>
       <c r="P126" s="1"/>
       <c r="Q126" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R126" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S126" s="1" t="s">
         <v>26</v>
@@ -12822,7 +12822,7 @@
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>438</v>
@@ -12845,7 +12845,7 @@
         <v>26</v>
       </c>
       <c r="T127" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U127" s="1" t="s">
         <v>732</v>
@@ -12864,10 +12864,10 @@
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
       <c r="E128" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G128" s="1"/>
       <c r="H128" s="1"/>
@@ -12879,11 +12879,11 @@
         <v>575</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M128" s="1"/>
       <c r="N128" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="O128" s="1" t="s">
         <v>736</v>
@@ -12893,7 +12893,7 @@
         <v>51</v>
       </c>
       <c r="R128" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S128" s="1" t="s">
         <v>26</v>
@@ -12955,7 +12955,7 @@
         <v>51</v>
       </c>
       <c r="R129" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S129" s="1" t="s">
         <v>26</v>
@@ -12980,7 +12980,7 @@
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
       <c r="E130" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>748</v>
@@ -12997,7 +12997,7 @@
         <v>59</v>
       </c>
       <c r="L130" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M130" s="1" t="s">
         <v>751</v>
@@ -13013,7 +13013,7 @@
         <v>101</v>
       </c>
       <c r="R130" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S130" s="1" t="s">
         <v>26</v>
@@ -13052,10 +13052,10 @@
         <v>757</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M131" s="1" t="s">
         <v>758</v>
@@ -13071,7 +13071,7 @@
         <v>51</v>
       </c>
       <c r="R131" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S131" s="1" t="s">
         <v>26</v>
@@ -13113,7 +13113,7 @@
         <v>765</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M132" s="1"/>
       <c r="N132" s="1" t="s">
@@ -13124,10 +13124,10 @@
       </c>
       <c r="P132" s="1"/>
       <c r="Q132" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R132" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S132" s="1" t="s">
         <v>26</v>
@@ -13189,7 +13189,7 @@
         <v>51</v>
       </c>
       <c r="R133" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S133" s="1" t="s">
         <v>26</v>
@@ -13214,7 +13214,7 @@
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
       <c r="E134" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>438</v>
@@ -13244,10 +13244,10 @@
         <v>781</v>
       </c>
       <c r="Q134" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R134" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S134" s="1" t="s">
         <v>26</v>
@@ -13302,10 +13302,10 @@
         <v>788</v>
       </c>
       <c r="Q135" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R135" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S135" s="1" t="s">
         <v>26</v>
@@ -13330,7 +13330,7 @@
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>792</v>
@@ -13351,7 +13351,7 @@
         <v>795</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M136" s="1" t="s">
         <v>796</v>
@@ -13364,10 +13364,10 @@
       </c>
       <c r="P136" s="1"/>
       <c r="Q136" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R136" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S136" s="1" t="s">
         <v>26</v>
@@ -13392,10 +13392,10 @@
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>800</v>
@@ -13421,7 +13421,7 @@
         <v>26</v>
       </c>
       <c r="T137" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U137" s="1" t="s">
         <v>803</v>
@@ -13440,7 +13440,7 @@
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>806</v>
@@ -13454,7 +13454,7 @@
         <v>807</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L138" s="1" t="s">
         <v>808</v>
@@ -13471,7 +13471,7 @@
         <v>101</v>
       </c>
       <c r="R138" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S138" s="1" t="s">
         <v>26</v>
@@ -13525,7 +13525,7 @@
         <v>51</v>
       </c>
       <c r="R139" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S139" s="1" t="s">
         <v>26</v>
@@ -13550,7 +13550,7 @@
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
       <c r="E140" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>820</v>
@@ -13571,7 +13571,7 @@
         <v>59</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M140" s="1"/>
       <c r="N140" s="1" t="s">
@@ -13582,10 +13582,10 @@
       </c>
       <c r="P140" s="1"/>
       <c r="Q140" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R140" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S140" s="1" t="s">
         <v>26</v>
@@ -13635,7 +13635,7 @@
         <v>26</v>
       </c>
       <c r="T141" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U141" s="1" t="s">
         <v>828</v>
@@ -13677,7 +13677,7 @@
         <v>26</v>
       </c>
       <c r="T142" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U142" s="1" t="s">
         <v>831</v>
@@ -13723,7 +13723,7 @@
         <v>26</v>
       </c>
       <c r="T143" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U143" s="1" t="s">
         <v>831</v>
@@ -13742,7 +13742,7 @@
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>292</v>
@@ -13767,7 +13767,7 @@
         <v>26</v>
       </c>
       <c r="T144" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U144" s="1" t="s">
         <v>839</v>
@@ -13807,7 +13807,7 @@
         <v>455</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M145" s="1"/>
       <c r="N145" s="1" t="s">
@@ -13821,10 +13821,10 @@
         <v>101</v>
       </c>
       <c r="R145" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S145" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T145" s="1" t="s">
         <v>26</v>
@@ -13862,7 +13862,7 @@
         <v>848</v>
       </c>
       <c r="K146" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L146" s="1" t="s">
         <v>214</v>
@@ -13876,10 +13876,10 @@
       </c>
       <c r="P146" s="1"/>
       <c r="Q146" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R146" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S146" s="1" t="s">
         <v>26</v>
@@ -13908,13 +13908,13 @@
         <v>27</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H147" s="1" t="s">
         <v>851</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J147" s="1"/>
       <c r="K147" s="1"/>
@@ -13931,7 +13931,7 @@
         <v>26</v>
       </c>
       <c r="T147" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U147" s="1"/>
       <c r="V147" s="1" t="s">
@@ -13948,10 +13948,10 @@
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G148" s="1"/>
       <c r="H148" s="1"/>
@@ -13969,7 +13969,7 @@
         <v>856</v>
       </c>
       <c r="N148" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O148" s="1" t="s">
         <v>857</v>
@@ -13979,7 +13979,7 @@
         <v>101</v>
       </c>
       <c r="R148" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S148" s="1" t="s">
         <v>26</v>
@@ -14002,7 +14002,7 @@
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>438</v>
@@ -14014,10 +14014,10 @@
         <v>860</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M149" s="1" t="s">
         <v>861</v>
@@ -14030,10 +14030,10 @@
       </c>
       <c r="P149" s="1"/>
       <c r="Q149" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R149" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S149" s="1" t="s">
         <v>26</v>
@@ -14058,7 +14058,7 @@
         <v>865</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>292</v>
@@ -14087,7 +14087,7 @@
         <v>26</v>
       </c>
       <c r="T150" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U150" s="1"/>
       <c r="V150" s="1" t="s">
@@ -14118,10 +14118,10 @@
         <v>869</v>
       </c>
       <c r="K151" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M151" s="1"/>
       <c r="N151" s="1" t="s">
@@ -14132,10 +14132,10 @@
       </c>
       <c r="P151" s="1"/>
       <c r="Q151" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R151" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S151" s="1" t="s">
         <v>26</v>
@@ -14158,10 +14158,10 @@
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
       <c r="E152" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
@@ -14181,7 +14181,7 @@
         <v>26</v>
       </c>
       <c r="T152" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U152" s="1"/>
       <c r="V152" s="1" t="s">
@@ -14204,7 +14204,7 @@
         <v>27</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H153" s="1"/>
       <c r="I153" s="1"/>
@@ -14223,7 +14223,7 @@
         <v>26</v>
       </c>
       <c r="T153" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U153" s="1" t="s">
         <v>875</v>
@@ -14242,7 +14242,7 @@
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
       <c r="E154" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>292</v>
@@ -14270,10 +14270,10 @@
       </c>
       <c r="P154" s="1"/>
       <c r="Q154" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R154" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S154" s="1" t="s">
         <v>26</v>
@@ -14296,7 +14296,7 @@
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>884</v>
@@ -14311,7 +14311,7 @@
         <v>59</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M155" s="1" t="s">
         <v>886</v>
@@ -14327,7 +14327,7 @@
         <v>101</v>
       </c>
       <c r="R155" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S155" s="1" t="s">
         <v>26</v>
@@ -14375,7 +14375,7 @@
         <v>101</v>
       </c>
       <c r="R156" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S156" s="1" t="s">
         <v>26</v>
@@ -14398,7 +14398,7 @@
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
       <c r="E157" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>894</v>
@@ -14424,10 +14424,10 @@
       </c>
       <c r="P157" s="1"/>
       <c r="Q157" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R157" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S157" s="1" t="s">
         <v>26</v>
@@ -14450,10 +14450,10 @@
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
       <c r="E158" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
@@ -14473,7 +14473,7 @@
         <v>26</v>
       </c>
       <c r="T158" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U158" s="1"/>
       <c r="V158" s="1" t="s">
@@ -14490,10 +14490,10 @@
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
       <c r="E159" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>28</v>
@@ -14519,7 +14519,7 @@
         <v>26</v>
       </c>
       <c r="T159" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U159" s="1"/>
       <c r="V159" s="1" t="s">
@@ -14556,7 +14556,7 @@
         <v>905</v>
       </c>
       <c r="K160" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L160" s="1" t="s">
         <v>404</v>
@@ -14572,10 +14572,10 @@
       </c>
       <c r="P160" s="1"/>
       <c r="Q160" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R160" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S160" s="1" t="s">
         <v>26</v>
@@ -14623,7 +14623,7 @@
         <v>26</v>
       </c>
       <c r="T161" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U161" s="1"/>
       <c r="V161" s="1" t="s">
@@ -14652,10 +14652,10 @@
         <v>911</v>
       </c>
       <c r="K162" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M162" s="1" t="s">
         <v>912</v>
@@ -14668,10 +14668,10 @@
       </c>
       <c r="P162" s="1"/>
       <c r="Q162" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R162" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S162" s="1" t="s">
         <v>26</v>
@@ -14706,7 +14706,7 @@
         <v>916</v>
       </c>
       <c r="K163" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L163" s="1" t="s">
         <v>917</v>
@@ -14723,7 +14723,7 @@
         <v>101</v>
       </c>
       <c r="R163" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S163" s="1" t="s">
         <v>26</v>
@@ -14746,7 +14746,7 @@
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
       <c r="E164" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>806</v>
@@ -14771,7 +14771,7 @@
         <v>26</v>
       </c>
       <c r="T164" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U164" s="1"/>
       <c r="V164" s="1" t="s">
@@ -14788,7 +14788,7 @@
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
       <c r="E165" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>292</v>
@@ -14817,7 +14817,7 @@
         <v>26</v>
       </c>
       <c r="T165" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U165" s="1"/>
       <c r="V165" s="1" t="s">
@@ -14834,10 +14834,10 @@
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
       <c r="E166" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G166" s="1"/>
       <c r="H166" s="1"/>
@@ -14855,7 +14855,7 @@
         <v>931</v>
       </c>
       <c r="N166" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="O166" s="1" t="s">
         <v>932</v>
@@ -14865,7 +14865,7 @@
         <v>101</v>
       </c>
       <c r="R166" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S166" s="1" t="s">
         <v>26</v>
@@ -14906,10 +14906,10 @@
         <v>935</v>
       </c>
       <c r="K167" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M167" s="1" t="s">
         <v>936</v>
@@ -14922,10 +14922,10 @@
       </c>
       <c r="P167" s="1"/>
       <c r="Q167" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R167" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S167" s="1" t="s">
         <v>26</v>
@@ -14948,10 +14948,10 @@
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
       <c r="E168" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G168" s="1"/>
       <c r="H168" s="1"/>
@@ -14960,14 +14960,14 @@
         <v>940</v>
       </c>
       <c r="K168" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="L168" s="1" t="s">
         <v>941</v>
       </c>
       <c r="M168" s="1"/>
       <c r="N168" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="O168" s="1" t="s">
         <v>942</v>
@@ -14977,7 +14977,7 @@
         <v>101</v>
       </c>
       <c r="R168" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S168" s="1" t="s">
         <v>26</v>
@@ -15036,10 +15036,10 @@
       </c>
       <c r="P169" s="1"/>
       <c r="Q169" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R169" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S169" s="1" t="s">
         <v>26</v>
@@ -15076,10 +15076,10 @@
         <v>954</v>
       </c>
       <c r="K170" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M170" s="1"/>
       <c r="N170" s="1" t="s">
@@ -15090,10 +15090,10 @@
       </c>
       <c r="P170" s="1"/>
       <c r="Q170" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R170" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S170" s="1" t="s">
         <v>26</v>
@@ -15141,7 +15141,7 @@
         <v>26</v>
       </c>
       <c r="T171" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U171" s="1" t="s">
         <v>958</v>
@@ -15194,10 +15194,10 @@
       </c>
       <c r="P172" s="1"/>
       <c r="Q172" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R172" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S172" s="1" t="s">
         <v>26</v>
@@ -15222,7 +15222,7 @@
         <v>968</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>235</v>
@@ -15234,7 +15234,7 @@
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
       <c r="M173" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N173" s="1"/>
       <c r="O173" s="1"/>
@@ -15247,7 +15247,7 @@
         <v>26</v>
       </c>
       <c r="T173" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U173" s="1"/>
       <c r="V173" s="1" t="s">
@@ -15278,7 +15278,7 @@
         <v>972</v>
       </c>
       <c r="K174" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="L174" s="1" t="s">
         <v>973</v>
@@ -15292,13 +15292,13 @@
       </c>
       <c r="P174" s="1"/>
       <c r="Q174" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R174" s="1" t="s">
         <v>26</v>
       </c>
       <c r="S174" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T174" s="1" t="s">
         <v>26</v>
@@ -15365,7 +15365,7 @@
         <v>26</v>
       </c>
       <c r="T175" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U175" s="1"/>
       <c r="V175" s="1" t="s">
@@ -15401,7 +15401,7 @@
         <v>59</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M176" s="1" t="s">
         <v>987</v>
@@ -15414,10 +15414,10 @@
       </c>
       <c r="P176" s="1"/>
       <c r="Q176" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R176" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S176" s="1" t="s">
         <v>26</v>
@@ -15442,7 +15442,7 @@
         <v>993</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>792</v>
@@ -15459,7 +15459,7 @@
         <v>996</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M177" s="1" t="s">
         <v>997</v>
@@ -15475,7 +15475,7 @@
         <v>51</v>
       </c>
       <c r="R177" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S177" s="1" t="s">
         <v>26</v>
@@ -15500,7 +15500,7 @@
       <c r="C178" s="1"/>
       <c r="D178" s="1"/>
       <c r="E178" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>292</v>
@@ -15532,7 +15532,7 @@
         <v>26</v>
       </c>
       <c r="S178" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T178" s="1" t="s">
         <v>26</v>
@@ -15556,7 +15556,7 @@
         <v>1008</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>71</v>
@@ -15574,7 +15574,7 @@
       <c r="K179" s="1"/>
       <c r="L179" s="1"/>
       <c r="M179" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N179" s="1"/>
       <c r="O179" s="1"/>
@@ -15587,7 +15587,7 @@
         <v>26</v>
       </c>
       <c r="T179" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U179" s="1"/>
       <c r="V179" s="1" t="s">
@@ -15606,7 +15606,7 @@
         <v>1012</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>235</v>
@@ -15640,10 +15640,10 @@
       </c>
       <c r="P180" s="1"/>
       <c r="Q180" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R180" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S180" s="1" t="s">
         <v>26</v>
@@ -15668,7 +15668,7 @@
         <v>1020</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>820</v>
@@ -15697,7 +15697,7 @@
         <v>101</v>
       </c>
       <c r="R181" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S181" s="1" t="s">
         <v>26</v>
@@ -15735,7 +15735,7 @@
         <v>1027</v>
       </c>
       <c r="L182" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M182" s="1"/>
       <c r="N182" s="1" t="s">
@@ -15749,10 +15749,10 @@
         <v>51</v>
       </c>
       <c r="R182" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S182" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T182" s="1" t="s">
         <v>26</v>
@@ -15790,10 +15790,10 @@
         <v>1034</v>
       </c>
       <c r="K183" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L183" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M183" s="1" t="s">
         <v>1032</v>
@@ -15815,7 +15815,7 @@
         <v>26</v>
       </c>
       <c r="T183" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U183" s="1" t="s">
         <v>1036</v>
@@ -15836,7 +15836,7 @@
         <v>1039</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>292</v>
@@ -15855,7 +15855,7 @@
         <v>455</v>
       </c>
       <c r="L184" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M184" s="1" t="s">
         <v>1039</v>
@@ -15871,7 +15871,7 @@
         <v>101</v>
       </c>
       <c r="R184" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S184" s="1" t="s">
         <v>26</v>
@@ -15896,7 +15896,7 @@
         <v>1045</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>1046</v>
@@ -15933,7 +15933,7 @@
         <v>26</v>
       </c>
       <c r="T185" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U185" s="1" t="s">
         <v>1050</v>
@@ -15954,7 +15954,7 @@
         <v>1053</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>312</v>
@@ -15966,7 +15966,7 @@
       <c r="K186" s="1"/>
       <c r="L186" s="1"/>
       <c r="M186" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N186" s="1"/>
       <c r="O186" s="1"/>
@@ -15979,7 +15979,7 @@
         <v>26</v>
       </c>
       <c r="T186" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U186" s="1"/>
       <c r="V186" s="1" t="s">
@@ -15996,10 +15996,10 @@
       <c r="C187" s="1"/>
       <c r="D187" s="1"/>
       <c r="E187" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G187" s="1"/>
       <c r="H187" s="1"/>
@@ -16019,7 +16019,7 @@
         <v>26</v>
       </c>
       <c r="T187" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U187" s="1" t="s">
         <v>1056</v>
@@ -16057,7 +16057,7 @@
         <v>1062</v>
       </c>
       <c r="L188" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M188" s="1" t="s">
         <v>1059</v>
@@ -16070,10 +16070,10 @@
       </c>
       <c r="P188" s="1"/>
       <c r="Q188" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R188" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S188" s="1" t="s">
         <v>26</v>
@@ -16118,10 +16118,10 @@
         <v>1068</v>
       </c>
       <c r="K189" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M189" s="1" t="s">
         <v>1066</v>
@@ -16134,10 +16134,10 @@
       </c>
       <c r="P189" s="1"/>
       <c r="Q189" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R189" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S189" s="1" t="s">
         <v>26</v>
@@ -16168,13 +16168,13 @@
         <v>27</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H190" s="1" t="s">
         <v>1073</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J190" s="1" t="s">
         <v>1074</v>
@@ -16183,7 +16183,7 @@
         <v>1075</v>
       </c>
       <c r="L190" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M190" s="1" t="s">
         <v>1072</v>
@@ -16198,10 +16198,10 @@
         <v>1077</v>
       </c>
       <c r="Q190" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R190" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S190" s="1" t="s">
         <v>26</v>
@@ -16234,19 +16234,19 @@
         <v>27</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H191" s="1" t="s">
         <v>1082</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J191" s="1"/>
       <c r="K191" s="1"/>
       <c r="L191" s="1"/>
       <c r="M191" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N191" s="1"/>
       <c r="O191" s="1"/>
@@ -16259,7 +16259,7 @@
         <v>26</v>
       </c>
       <c r="T191" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U191" s="1"/>
       <c r="V191" s="1" t="s">
@@ -16278,7 +16278,7 @@
         <v>1085</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>235</v>
@@ -16306,10 +16306,10 @@
       </c>
       <c r="P192" s="1"/>
       <c r="Q192" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R192" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S192" s="1" t="s">
         <v>26</v>
@@ -16334,7 +16334,7 @@
         <v>1090</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>292</v>
@@ -16370,10 +16370,10 @@
         <v>1095</v>
       </c>
       <c r="Q193" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R193" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S193" s="1" t="s">
         <v>26</v>
@@ -16432,10 +16432,10 @@
       </c>
       <c r="P194" s="1"/>
       <c r="Q194" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R194" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S194" s="1" t="s">
         <v>26</v>
@@ -16497,7 +16497,7 @@
         <v>101</v>
       </c>
       <c r="R195" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S195" s="1" t="s">
         <v>26</v>
@@ -16522,7 +16522,7 @@
         <v>1113</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>1114</v>
@@ -16558,10 +16558,10 @@
         <v>1119</v>
       </c>
       <c r="Q196" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R196" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S196" s="1" t="s">
         <v>26</v>
@@ -16586,7 +16586,7 @@
         <v>1122</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>820</v>
@@ -16604,7 +16604,7 @@
       <c r="K197" s="1"/>
       <c r="L197" s="1"/>
       <c r="M197" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N197" s="1"/>
       <c r="O197" s="1"/>
@@ -16617,7 +16617,7 @@
         <v>26</v>
       </c>
       <c r="T197" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U197" s="1"/>
       <c r="V197" s="1" t="s">
@@ -16650,10 +16650,10 @@
         <v>1127</v>
       </c>
       <c r="K198" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L198" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M198" s="1" t="s">
         <v>1125</v>
@@ -16669,7 +16669,7 @@
         <v>101</v>
       </c>
       <c r="R198" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S198" s="1" t="s">
         <v>26</v>
@@ -16712,7 +16712,7 @@
         <v>1134</v>
       </c>
       <c r="K199" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L199" s="1" t="s">
         <v>214</v>
@@ -16728,10 +16728,10 @@
       </c>
       <c r="P199" s="1"/>
       <c r="Q199" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R199" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S199" s="1" t="s">
         <v>26</v>
@@ -16766,7 +16766,7 @@
         <v>1139</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J200" s="1" t="s">
         <v>1140</v>
@@ -16791,7 +16791,7 @@
         <v>101</v>
       </c>
       <c r="R200" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S200" s="1" t="s">
         <v>26</v>
@@ -16816,7 +16816,7 @@
         <v>1145</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>71</v>
@@ -16830,7 +16830,7 @@
         <v>1147</v>
       </c>
       <c r="K201" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L201" s="1"/>
       <c r="M201" s="1" t="s">
@@ -16855,7 +16855,7 @@
         <v>26</v>
       </c>
       <c r="T201" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U201" s="1"/>
       <c r="V201" s="1" t="s">
@@ -16874,7 +16874,7 @@
         <v>1152</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>1153</v>
@@ -16892,7 +16892,7 @@
         <v>1155</v>
       </c>
       <c r="K202" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="L202" s="1" t="s">
         <v>1156</v>
@@ -16908,10 +16908,10 @@
       </c>
       <c r="P202" s="1"/>
       <c r="Q202" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R202" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S202" s="1" t="s">
         <v>26</v>
@@ -16950,7 +16950,7 @@
         <v>1163</v>
       </c>
       <c r="K203" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L203" s="1"/>
       <c r="M203" s="1" t="s">
@@ -16964,10 +16964,10 @@
       </c>
       <c r="P203" s="1"/>
       <c r="Q203" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R203" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S203" s="1" t="s">
         <v>26</v>
@@ -16998,13 +16998,13 @@
         <v>27</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I204" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J204" s="1" t="s">
         <v>1168</v>
@@ -17013,7 +17013,7 @@
         <v>59</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M204" s="1" t="s">
         <v>1167</v>
@@ -17029,7 +17029,7 @@
         <v>101</v>
       </c>
       <c r="R204" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S204" s="1" t="s">
         <v>26</v>
@@ -17054,7 +17054,7 @@
         <v>1172</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>235</v>
@@ -17066,7 +17066,7 @@
         <v>1173</v>
       </c>
       <c r="K205" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L205" s="1" t="s">
         <v>564</v>
@@ -17085,7 +17085,7 @@
         <v>51</v>
       </c>
       <c r="R205" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S205" s="1" t="s">
         <v>26</v>
@@ -17110,7 +17110,7 @@
         <v>1177</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>662</v>
@@ -17147,7 +17147,7 @@
         <v>51</v>
       </c>
       <c r="R206" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S206" s="1" t="s">
         <v>26</v>
@@ -17172,7 +17172,7 @@
         <v>1184</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>1185</v>
@@ -17207,7 +17207,7 @@
         <v>101</v>
       </c>
       <c r="R207" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S207" s="1" t="s">
         <v>26</v>
@@ -17250,7 +17250,7 @@
         <v>1194</v>
       </c>
       <c r="K208" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L208" s="1" t="s">
         <v>1195</v>
@@ -17266,10 +17266,10 @@
       </c>
       <c r="P208" s="1"/>
       <c r="Q208" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R208" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S208" s="1" t="s">
         <v>26</v>
@@ -17371,7 +17371,7 @@
         <v>59</v>
       </c>
       <c r="L210" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M210" s="1"/>
       <c r="N210" s="1" t="s">
@@ -17385,7 +17385,7 @@
         <v>101</v>
       </c>
       <c r="R210" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S210" s="1" t="s">
         <v>26</v>
@@ -17418,14 +17418,14 @@
         <v>27</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="H211" s="1" t="s">
         <v>1214</v>
       </c>
       <c r="I211" s="1"/>
       <c r="J211" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K211" s="1" t="s">
         <v>59</v>
@@ -17444,10 +17444,10 @@
       </c>
       <c r="P211" s="1"/>
       <c r="Q211" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R211" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S211" s="1" t="s">
         <v>26</v>
@@ -17488,10 +17488,10 @@
         <v>1221</v>
       </c>
       <c r="K212" s="1" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="L212" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M212" s="1" t="s">
         <v>1222</v>
@@ -17507,7 +17507,7 @@
         <v>101</v>
       </c>
       <c r="R212" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S212" s="1" t="s">
         <v>26</v>
@@ -17532,7 +17532,7 @@
         <v>1226</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>292</v>
@@ -17571,7 +17571,7 @@
         <v>26</v>
       </c>
       <c r="T213" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U213" s="1" t="s">
         <v>1036</v>
@@ -17594,7 +17594,7 @@
         <v>1234</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>1235</v>
@@ -17629,7 +17629,7 @@
         <v>101</v>
       </c>
       <c r="R214" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S214" s="1" t="s">
         <v>26</v>
@@ -17658,7 +17658,7 @@
         <v>1244</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>1235</v>
@@ -17689,7 +17689,7 @@
         <v>101</v>
       </c>
       <c r="R215" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S215" s="1" t="s">
         <v>26</v>
@@ -17716,10 +17716,10 @@
         <v>1253</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G216" s="1" t="s">
         <v>1254</v>
@@ -17739,17 +17739,17 @@
         <v>1253</v>
       </c>
       <c r="N216" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="O216" s="1" t="s">
         <v>1257</v>
       </c>
       <c r="P216" s="1"/>
       <c r="Q216" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R216" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S216" s="1" t="s">
         <v>26</v>
@@ -17778,19 +17778,19 @@
         <v>1253</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H217" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I217" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J217" s="1" t="s">
         <v>1255</v>
@@ -17805,20 +17805,20 @@
         <v>1253</v>
       </c>
       <c r="N217" s="1" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="O217" s="1" t="s">
         <v>1257</v>
       </c>
       <c r="P217" s="1"/>
       <c r="Q217" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R217" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S217" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T217" s="1" t="s">
         <v>26</v>
@@ -17872,10 +17872,10 @@
       </c>
       <c r="P218" s="1"/>
       <c r="Q218" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R218" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S218" s="1" t="s">
         <v>26</v>
@@ -17920,10 +17920,10 @@
         <v>1273</v>
       </c>
       <c r="K219" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L219" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M219" s="1" t="s">
         <v>1274</v>
@@ -17936,10 +17936,10 @@
       </c>
       <c r="P219" s="1"/>
       <c r="Q219" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R219" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S219" s="1" t="s">
         <v>26</v>
@@ -17966,7 +17966,7 @@
         <v>1279</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>1185</v>
@@ -17997,7 +17997,7 @@
         <v>101</v>
       </c>
       <c r="R220" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S220" s="1" t="s">
         <v>26</v>
@@ -18024,7 +18024,7 @@
         <v>1282</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>1185</v>
@@ -18059,7 +18059,7 @@
         <v>101</v>
       </c>
       <c r="R221" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S221" s="1" t="s">
         <v>26</v>
@@ -18088,7 +18088,7 @@
         <v>1288</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>1153</v>
@@ -18102,7 +18102,7 @@
       <c r="K222" s="1"/>
       <c r="L222" s="1"/>
       <c r="M222" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N222" s="1"/>
       <c r="O222" s="1"/>
@@ -18115,7 +18115,7 @@
         <v>26</v>
       </c>
       <c r="T222" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U222" s="1"/>
       <c r="V222" s="1" t="s">
@@ -18136,13 +18136,13 @@
         <v>1288</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>1153</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H223" s="1"/>
       <c r="I223" s="1"/>
@@ -18169,7 +18169,7 @@
         <v>51</v>
       </c>
       <c r="R223" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S223" s="1" t="s">
         <v>26</v>
@@ -18217,7 +18217,7 @@
         <v>1299</v>
       </c>
       <c r="L224" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M224" s="1" t="s">
         <v>1300</v>
@@ -18230,10 +18230,10 @@
       </c>
       <c r="P224" s="1"/>
       <c r="Q224" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R224" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S224" s="1" t="s">
         <v>26</v>
@@ -18277,7 +18277,7 @@
         <v>1307</v>
       </c>
       <c r="L225" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M225" s="1" t="s">
         <v>1308</v>
@@ -18293,7 +18293,7 @@
         <v>51</v>
       </c>
       <c r="R225" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S225" s="1" t="s">
         <v>26</v>
@@ -18335,7 +18335,7 @@
         <v>1027</v>
       </c>
       <c r="L226" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M226" s="1" t="s">
         <v>1313</v>
@@ -18348,13 +18348,13 @@
       </c>
       <c r="P226" s="1"/>
       <c r="Q226" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R226" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S226" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T226" s="1" t="s">
         <v>26</v>
@@ -18395,7 +18395,7 @@
         <v>1027</v>
       </c>
       <c r="L227" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M227" s="1" t="s">
         <v>1318</v>
@@ -18408,13 +18408,13 @@
       </c>
       <c r="P227" s="1"/>
       <c r="Q227" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R227" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S227" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T227" s="1" t="s">
         <v>26</v>
@@ -18475,10 +18475,10 @@
         <v>51</v>
       </c>
       <c r="R228" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S228" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T228" s="1" t="s">
         <v>26</v>
@@ -18535,10 +18535,10 @@
         <v>51</v>
       </c>
       <c r="R229" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S229" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T229" s="1" t="s">
         <v>26</v>
@@ -18599,10 +18599,10 @@
         <v>51</v>
       </c>
       <c r="R230" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S230" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T230" s="1" t="s">
         <v>26</v>
@@ -18658,10 +18658,10 @@
       </c>
       <c r="P231" s="1"/>
       <c r="Q231" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R231" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S231" s="1" t="s">
         <v>26</v>
@@ -18721,7 +18721,7 @@
         <v>101</v>
       </c>
       <c r="R232" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S232" s="1" t="s">
         <v>26</v>
@@ -18779,7 +18779,7 @@
         <v>51</v>
       </c>
       <c r="R233" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S233" s="1" t="s">
         <v>26</v>
@@ -18788,7 +18788,7 @@
         <v>26</v>
       </c>
       <c r="U233" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V233" s="1" t="s">
         <v>1363</v>
@@ -18824,10 +18824,10 @@
         <v>1368</v>
       </c>
       <c r="K234" s="1" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M234" s="1" t="s">
         <v>1369</v>
@@ -18843,13 +18843,13 @@
         <v>51</v>
       </c>
       <c r="R234" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S234" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T234" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U234" s="1" t="s">
         <v>1371</v>
@@ -18878,13 +18878,13 @@
         <v>27</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H235" s="1" t="s">
         <v>1375</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J235" s="1" t="s">
         <v>1376</v>
@@ -18909,7 +18909,7 @@
         <v>101</v>
       </c>
       <c r="R235" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S235" s="1" t="s">
         <v>26</v>
@@ -18959,7 +18959,7 @@
         <v>518</v>
       </c>
       <c r="L236" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M236" s="1" t="s">
         <v>1385</v>
@@ -18975,7 +18975,7 @@
         <v>101</v>
       </c>
       <c r="R236" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S236" s="1" t="s">
         <v>26</v>
@@ -19040,10 +19040,10 @@
         <v>1395</v>
       </c>
       <c r="Q237" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R237" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S237" s="1" t="s">
         <v>26</v>
@@ -19091,7 +19091,7 @@
         <v>1401</v>
       </c>
       <c r="L238" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M238" s="1" t="s">
         <v>1402</v>
@@ -19107,7 +19107,7 @@
         <v>51</v>
       </c>
       <c r="R238" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S238" s="1" t="s">
         <v>26</v>
@@ -19152,7 +19152,7 @@
         <v>1409</v>
       </c>
       <c r="K239" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="L239" s="1" t="s">
         <v>1410</v>
@@ -19171,7 +19171,7 @@
         <v>51</v>
       </c>
       <c r="R239" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S239" s="1" t="s">
         <v>26</v>
@@ -19216,7 +19216,7 @@
         <v>1419</v>
       </c>
       <c r="K240" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L240" s="1" t="s">
         <v>1361</v>
@@ -19235,13 +19235,13 @@
         <v>101</v>
       </c>
       <c r="R240" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S240" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T240" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U240" s="1" t="s">
         <v>1422</v>
@@ -19293,7 +19293,7 @@
         <v>101</v>
       </c>
       <c r="R241" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S241" s="1" t="s">
         <v>26</v>
@@ -19353,7 +19353,7 @@
         <v>51</v>
       </c>
       <c r="R242" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S242" s="1" t="s">
         <v>26</v>
@@ -19382,7 +19382,7 @@
         <v>1340</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>220</v>
@@ -19412,10 +19412,10 @@
       </c>
       <c r="P243" s="1"/>
       <c r="Q243" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R243" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S243" s="1" t="s">
         <v>26</v>
@@ -19476,10 +19476,10 @@
       </c>
       <c r="P244" s="1"/>
       <c r="Q244" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R244" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S244" s="1" t="s">
         <v>26</v>
@@ -19540,10 +19540,10 @@
       </c>
       <c r="P245" s="1"/>
       <c r="Q245" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R245" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S245" s="1" t="s">
         <v>26</v>
@@ -19606,10 +19606,10 @@
         <v>26</v>
       </c>
       <c r="S246" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="T246" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U246" s="1" t="s">
         <v>62</v>
@@ -19644,10 +19644,10 @@
         <v>1462</v>
       </c>
       <c r="K247" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="M247" s="1" t="s">
         <v>1461</v>
@@ -19663,7 +19663,7 @@
         <v>101</v>
       </c>
       <c r="R247" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S247" s="1" t="s">
         <v>26</v>
@@ -19704,10 +19704,10 @@
         <v>1468</v>
       </c>
       <c r="K248" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M248" s="1" t="s">
         <v>1467</v>
@@ -19720,10 +19720,10 @@
       </c>
       <c r="P248" s="1"/>
       <c r="Q248" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R248" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S248" s="1" t="s">
         <v>26</v>
@@ -19756,22 +19756,22 @@
         <v>27</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H249" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J249" s="1" t="s">
         <v>1468</v>
       </c>
       <c r="K249" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M249" s="1" t="s">
         <v>1472</v>
@@ -19784,10 +19784,10 @@
       </c>
       <c r="P249" s="1"/>
       <c r="Q249" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R249" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S249" s="1" t="s">
         <v>26</v>
@@ -19833,7 +19833,7 @@
         <v>1480</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M250" s="1" t="s">
         <v>1476</v>
@@ -19846,10 +19846,10 @@
       </c>
       <c r="P250" s="1"/>
       <c r="Q250" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R250" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S250" s="1" t="s">
         <v>26</v>
@@ -19913,13 +19913,13 @@
         <v>51</v>
       </c>
       <c r="R251" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S251" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T251" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U251" s="1" t="s">
         <v>1371</v>
@@ -19956,10 +19956,10 @@
         <v>1497</v>
       </c>
       <c r="K252" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M252" s="1" t="s">
         <v>1495</v>
@@ -19975,7 +19975,7 @@
         <v>101</v>
       </c>
       <c r="R252" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S252" s="1" t="s">
         <v>26</v>
@@ -20016,10 +20016,10 @@
         <v>1501</v>
       </c>
       <c r="K253" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M253" s="1" t="s">
         <v>1495</v>
@@ -20035,7 +20035,7 @@
         <v>101</v>
       </c>
       <c r="R253" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S253" s="1" t="s">
         <v>26</v>
@@ -20097,7 +20097,7 @@
         <v>101</v>
       </c>
       <c r="R254" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S254" s="1" t="s">
         <v>26</v>
@@ -20106,7 +20106,7 @@
         <v>26</v>
       </c>
       <c r="U254" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V254" s="1" t="s">
         <v>1512</v>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="P255" s="1"/>
       <c r="Q255" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R255" s="1" t="s">
         <v>26</v>
@@ -20198,10 +20198,10 @@
         <v>1524</v>
       </c>
       <c r="K256" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L256" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M256" s="1" t="s">
         <v>1523</v>
@@ -20214,10 +20214,10 @@
       </c>
       <c r="P256" s="1"/>
       <c r="Q256" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R256" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S256" s="1" t="s">
         <v>26</v>
@@ -20258,10 +20258,10 @@
         <v>1524</v>
       </c>
       <c r="K257" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L257" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M257" s="1" t="s">
         <v>1528</v>
@@ -20274,10 +20274,10 @@
       </c>
       <c r="P257" s="1"/>
       <c r="Q257" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R257" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S257" s="1" t="s">
         <v>26</v>
@@ -20320,7 +20320,7 @@
         <v>1534</v>
       </c>
       <c r="K258" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L258" s="1" t="s">
         <v>1531</v>
@@ -20336,10 +20336,10 @@
       </c>
       <c r="P258" s="1"/>
       <c r="Q258" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R258" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S258" s="1" t="s">
         <v>26</v>
@@ -20378,7 +20378,7 @@
         <v>1534</v>
       </c>
       <c r="K259" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L259" s="1"/>
       <c r="M259" s="1" t="s">
@@ -20394,7 +20394,7 @@
         <v>1540</v>
       </c>
       <c r="Q259" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R259" s="1" t="s">
         <v>26</v>
@@ -20403,7 +20403,7 @@
         <v>26</v>
       </c>
       <c r="T259" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U259" s="1" t="s">
         <v>658</v>
@@ -20454,10 +20454,10 @@
       </c>
       <c r="P260" s="1"/>
       <c r="Q260" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R260" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S260" s="1" t="s">
         <v>26</v>
@@ -20514,10 +20514,10 @@
       </c>
       <c r="P261" s="1"/>
       <c r="Q261" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R261" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S261" s="1" t="s">
         <v>26</v>
@@ -20581,7 +20581,7 @@
         <v>101</v>
       </c>
       <c r="R262" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S262" s="1" t="s">
         <v>26</v>
@@ -20643,7 +20643,7 @@
         <v>101</v>
       </c>
       <c r="R263" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S263" s="1" t="s">
         <v>26</v>
@@ -20672,7 +20672,7 @@
         <v>1572</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>1573</v>
@@ -20706,10 +20706,10 @@
       </c>
       <c r="P264" s="1"/>
       <c r="Q264" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R264" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S264" s="1" t="s">
         <v>26</v>
@@ -20736,7 +20736,7 @@
         <v>1579</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>1580</v>
@@ -20767,7 +20767,7 @@
         <v>101</v>
       </c>
       <c r="R265" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S265" s="1" t="s">
         <v>26</v>
@@ -20806,10 +20806,10 @@
         <v>1588</v>
       </c>
       <c r="K266" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M266" s="1" t="s">
         <v>1589</v>
@@ -20822,10 +20822,10 @@
       </c>
       <c r="P266" s="1"/>
       <c r="Q266" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R266" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S266" s="1" t="s">
         <v>26</v>
@@ -20860,13 +20860,13 @@
         <v>27</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H267" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I267" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J267" s="1" t="s">
         <v>1594</v>
@@ -20891,7 +20891,7 @@
         <v>51</v>
       </c>
       <c r="R267" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S267" s="1" t="s">
         <v>26</v>
@@ -20939,7 +20939,7 @@
         <v>1605</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="M268" s="1" t="s">
         <v>1606</v>
@@ -20955,7 +20955,7 @@
         <v>101</v>
       </c>
       <c r="R268" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S268" s="1" t="s">
         <v>26</v>
@@ -20964,7 +20964,7 @@
         <v>26</v>
       </c>
       <c r="U268" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V268" s="1" t="s">
         <v>1608</v>
@@ -21015,7 +21015,7 @@
         <v>101</v>
       </c>
       <c r="R269" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S269" s="1" t="s">
         <v>26</v>
@@ -21076,10 +21076,10 @@
       </c>
       <c r="P270" s="1"/>
       <c r="Q270" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R270" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S270" s="1" t="s">
         <v>26</v>
@@ -21138,10 +21138,10 @@
       </c>
       <c r="P271" s="1"/>
       <c r="Q271" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R271" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S271" s="1" t="s">
         <v>26</v>
@@ -21189,7 +21189,7 @@
         <v>59</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M272" s="1" t="s">
         <v>1630</v>
@@ -21202,7 +21202,7 @@
       </c>
       <c r="P272" s="1"/>
       <c r="Q272" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R272" s="1" t="s">
         <v>26</v>
@@ -21211,7 +21211,7 @@
         <v>26</v>
       </c>
       <c r="T272" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U272" s="1" t="s">
         <v>1636</v>
@@ -21253,7 +21253,7 @@
         <v>59</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M273" s="1" t="s">
         <v>1639</v>
@@ -21266,10 +21266,10 @@
       </c>
       <c r="P273" s="1"/>
       <c r="Q273" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R273" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S273" s="1" t="s">
         <v>26</v>
@@ -21296,19 +21296,19 @@
         <v>1645</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>220</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H274" s="1" t="s">
         <v>1646</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J274" s="1" t="s">
         <v>1647</v>
@@ -21335,7 +21335,7 @@
         <v>101</v>
       </c>
       <c r="R274" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S274" s="1" t="s">
         <v>26</v>
@@ -21362,19 +21362,19 @@
         <v>1653</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>220</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H275" s="1" t="s">
         <v>1646</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J275" s="1" t="s">
         <v>1647</v>
@@ -21401,7 +21401,7 @@
         <v>101</v>
       </c>
       <c r="R275" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S275" s="1" t="s">
         <v>26</v>
@@ -21463,7 +21463,7 @@
         <v>51</v>
       </c>
       <c r="R276" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S276" s="1" t="s">
         <v>26</v>
@@ -21472,7 +21472,7 @@
         <v>26</v>
       </c>
       <c r="U276" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V276" s="1" t="s">
         <v>1663</v>
@@ -21527,7 +21527,7 @@
         <v>101</v>
       </c>
       <c r="R277" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S277" s="1" t="s">
         <v>26</v>
@@ -21536,7 +21536,7 @@
         <v>26</v>
       </c>
       <c r="U277" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V277" s="1" t="s">
         <v>1670</v>
@@ -21556,7 +21556,7 @@
         <v>1282</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>1248</v>
@@ -21591,7 +21591,7 @@
         <v>101</v>
       </c>
       <c r="R278" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S278" s="1" t="s">
         <v>26</v>
@@ -21620,7 +21620,7 @@
         <v>1677</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>1248</v>
@@ -21651,7 +21651,7 @@
         <v>101</v>
       </c>
       <c r="R279" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S279" s="1" t="s">
         <v>26</v>
@@ -21692,7 +21692,7 @@
         <v>1683</v>
       </c>
       <c r="K280" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L280" s="1" t="s">
         <v>214</v>
@@ -21708,10 +21708,10 @@
       </c>
       <c r="P280" s="1"/>
       <c r="Q280" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R280" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S280" s="1" t="s">
         <v>26</v>
@@ -21771,7 +21771,7 @@
         <v>51</v>
       </c>
       <c r="R281" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S281" s="1" t="s">
         <v>26</v>
@@ -21830,10 +21830,10 @@
       </c>
       <c r="P282" s="1"/>
       <c r="Q282" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R282" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S282" s="1" t="s">
         <v>26</v>
@@ -21897,7 +21897,7 @@
         <v>51</v>
       </c>
       <c r="R283" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S283" s="1" t="s">
         <v>26</v>
@@ -21906,7 +21906,7 @@
         <v>26</v>
       </c>
       <c r="U283" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V283" s="1" t="s">
         <v>1709</v>
@@ -21956,10 +21956,10 @@
       </c>
       <c r="P284" s="1"/>
       <c r="Q284" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="R284" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S284" s="1" t="s">
         <v>26</v>
@@ -21968,7 +21968,7 @@
         <v>26</v>
       </c>
       <c r="U284" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="V284" s="1" t="s">
         <v>1719</v>
@@ -21988,7 +21988,7 @@
         <v>1721</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>71</v>
@@ -22000,7 +22000,7 @@
       <c r="K285" s="1"/>
       <c r="L285" s="1"/>
       <c r="M285" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="N285" s="1"/>
       <c r="O285" s="1"/>
@@ -22013,7 +22013,7 @@
         <v>26</v>
       </c>
       <c r="T285" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U285" s="1"/>
       <c r="V285" s="1" t="s">
@@ -22067,13 +22067,13 @@
         <v>51</v>
       </c>
       <c r="R286" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S286" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T286" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U286" s="1" t="s">
         <v>1732</v>
@@ -22135,7 +22135,7 @@
         <v>51</v>
       </c>
       <c r="R287" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="S287" s="1" t="s">
         <v>26</v>
